--- a/docs/downloads/05/tbl_latrine_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/05/tbl_latrine_marovoay_ampijoroa.xlsx
@@ -495,12 +495,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -512,12 +506,6 @@
         <is>
           <t>Fosse septique en individuel</t>
         </is>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>
